--- a/港岛-香港仔及鸭脷洲-PORTO/PORTO_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-PORTO/PORTO_销控明细表.xlsx
@@ -271,10 +271,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -4927,34 +4927,34 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
-        <v>13648000</v>
+        <v>11396000</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>31303</v>
+        <v>26138</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="5" t="n">
-        <v>11396080</v>
+        <v>11396000</v>
       </c>
       <c r="L67" s="5" t="n">
         <v>26138</v>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
@@ -6229,34 +6229,34 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
-        <v>12783000</v>
+        <v>10674000</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>29319</v>
+        <v>24482</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="5" t="n">
-        <v>10673805</v>
+        <v>10674000</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>24481</v>
+        <v>24482</v>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J99" s="3" t="inlineStr">
@@ -6936,12 +6936,12 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L99" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M99" s="3" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="N99" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I169" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J169" s="3" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L169" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M169" s="3" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="N169" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -11345,7 +11345,7 @@
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
@@ -11355,12 +11355,12 @@
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I170" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J170" s="3" t="inlineStr">
@@ -11370,12 +11370,12 @@
       </c>
       <c r="K170" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L170" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M170" s="3" t="inlineStr">
@@ -11385,7 +11385,7 @@
       </c>
       <c r="N170" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -11415,7 +11415,7 @@
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
@@ -11425,12 +11425,12 @@
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I171" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J171" s="3" t="inlineStr">
@@ -11440,12 +11440,12 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L171" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M171" s="3" t="inlineStr">
@@ -11455,7 +11455,7 @@
       </c>
       <c r="N171" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
@@ -11565,12 +11565,12 @@
       </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I173" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J173" s="3" t="inlineStr">
@@ -11580,12 +11580,12 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L173" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M173" s="3" t="inlineStr">
@@ -11595,7 +11595,7 @@
       </c>
       <c r="N173" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -11625,7 +11625,7 @@
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
@@ -11635,12 +11635,12 @@
       </c>
       <c r="H174" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I174" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J174" s="3" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L174" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M174" s="3" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="N174" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -11886,7 +11886,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>68</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -11965,12 +11965,49 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 746呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 644呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+      <c r="I5" s="21" t="inlineStr"/>
+      <c r="J5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 286呎 (1房)
 -
@@ -11978,49 +12015,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr"/>
-      <c r="F5" s="20" t="inlineStr"/>
-      <c r="G5" s="20" t="inlineStr"/>
-      <c r="H5" s="20" t="inlineStr"/>
-      <c r="I5" s="20" t="inlineStr"/>
-      <c r="J5" s="20" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>28&amp;29</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 746呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>D | 644呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+      <c r="I6" s="21" t="inlineStr"/>
+      <c r="J6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -12028,7 +12028,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12044,7 +12044,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12068,7 +12068,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12076,7 +12076,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12084,8 +12084,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr"/>
-      <c r="J7" s="20" t="inlineStr"/>
+      <c r="I7" s="21" t="inlineStr"/>
+      <c r="J7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -12093,7 +12093,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12109,7 +12109,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12133,7 +12133,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12141,7 +12141,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12149,8 +12149,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I8" s="20" t="inlineStr"/>
-      <c r="J8" s="20" t="inlineStr"/>
+      <c r="I8" s="21" t="inlineStr"/>
+      <c r="J8" s="21" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -12174,7 +12174,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12198,7 +12198,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12206,7 +12206,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12214,8 +12214,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr"/>
-      <c r="J9" s="20" t="inlineStr"/>
+      <c r="I9" s="21" t="inlineStr"/>
+      <c r="J9" s="21" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -12263,7 +12263,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12271,7 +12271,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12279,8 +12279,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I10" s="20" t="inlineStr"/>
-      <c r="J10" s="20" t="inlineStr"/>
+      <c r="I10" s="21" t="inlineStr"/>
+      <c r="J10" s="21" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -12328,7 +12328,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12336,7 +12336,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12344,8 +12344,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I11" s="20" t="inlineStr"/>
-      <c r="J11" s="20" t="inlineStr"/>
+      <c r="I11" s="21" t="inlineStr"/>
+      <c r="J11" s="21" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -12393,7 +12393,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12401,7 +12401,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12409,8 +12409,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr"/>
-      <c r="J12" s="20" t="inlineStr"/>
+      <c r="I12" s="21" t="inlineStr"/>
+      <c r="J12" s="21" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -12466,7 +12466,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12474,8 +12474,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I13" s="20" t="inlineStr"/>
-      <c r="J13" s="20" t="inlineStr"/>
+      <c r="I13" s="21" t="inlineStr"/>
+      <c r="J13" s="21" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -12531,7 +12531,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H14" s="21" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12539,8 +12539,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I14" s="20" t="inlineStr"/>
-      <c r="J14" s="20" t="inlineStr"/>
+      <c r="I14" s="21" t="inlineStr"/>
+      <c r="J14" s="21" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -12564,12 +12564,12 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="24" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
-$1365万
-$31,303/呎
-(在售)</t>
+$1140万
+$26,138/呎
+(26年-09月-12日)</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -12604,8 +12604,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I15" s="20" t="inlineStr"/>
-      <c r="J15" s="20" t="inlineStr"/>
+      <c r="I15" s="21" t="inlineStr"/>
+      <c r="J15" s="21" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -12669,8 +12669,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I16" s="20" t="inlineStr"/>
-      <c r="J16" s="20" t="inlineStr"/>
+      <c r="I16" s="21" t="inlineStr"/>
+      <c r="J16" s="21" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -12734,8 +12734,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I17" s="20" t="inlineStr"/>
-      <c r="J17" s="20" t="inlineStr"/>
+      <c r="I17" s="21" t="inlineStr"/>
+      <c r="J17" s="21" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -12759,12 +12759,12 @@
 (26年-06月-08日)</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
-$1278万
-$29,319/呎
-(在售)</t>
+$1067万
+$24,482/呎
+(26年-09月-13日)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -12799,8 +12799,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I18" s="20" t="inlineStr"/>
-      <c r="J18" s="20" t="inlineStr"/>
+      <c r="I18" s="21" t="inlineStr"/>
+      <c r="J18" s="21" t="inlineStr"/>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
@@ -12864,8 +12864,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I19" s="20" t="inlineStr"/>
-      <c r="J19" s="20" t="inlineStr"/>
+      <c r="I19" s="21" t="inlineStr"/>
+      <c r="J19" s="21" t="inlineStr"/>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
@@ -12905,7 +12905,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 296呎 (1房)
 -
@@ -12913,12 +12913,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="G20" s="23" t="inlineStr">
         <is>
           <t>F | 346呎 (2房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -12929,8 +12929,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I20" s="20" t="inlineStr"/>
-      <c r="J20" s="20" t="inlineStr"/>
+      <c r="I20" s="21" t="inlineStr"/>
+      <c r="J20" s="21" t="inlineStr"/>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
@@ -13491,7 +13491,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 350呎 (2房)
 -
@@ -13499,7 +13499,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 204呎 (1房)
 -
@@ -13507,23 +13507,23 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>C | 401呎 (2房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>D | 234呎 (1房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="E28" s="21" t="inlineStr">
-        <is>
-          <t>D | 234呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F28" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 238呎 (1房)
 -
@@ -13531,31 +13531,31 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G28" s="21" t="inlineStr">
+      <c r="G28" s="23" t="inlineStr">
         <is>
           <t>F | 250呎 (1房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="H28" s="23" t="inlineStr">
+        <is>
+          <t>G | 240呎 (1房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="H28" s="21" t="inlineStr">
-        <is>
-          <t>G | 240呎 (1房)
+(在售)</t>
+        </is>
+      </c>
+      <c r="I28" s="23" t="inlineStr">
+        <is>
+          <t>H | 192呎 (开放式)
+招标单位
 -
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I28" s="21" t="inlineStr">
-        <is>
-          <t>H | 192呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J28" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="J28" s="20" t="inlineStr">
         <is>
           <t>J | 199呎 (开放式)
 -

--- a/港岛-香港仔及鸭脷洲-PORTO/PORTO_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-PORTO/PORTO_销控明细表.xlsx
@@ -271,10 +271,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -11555,38 +11555,30 @@
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H173" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I173" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H173" s="5" t="n">
+        <v>6225000</v>
+      </c>
+      <c r="I173" s="5" t="n">
+        <v>26603</v>
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K173" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L173" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K173" s="5" t="n">
+        <v>6225000</v>
+      </c>
+      <c r="L173" s="5" t="n">
+        <v>26603</v>
       </c>
       <c r="M173" s="3" t="inlineStr">
         <is>
@@ -11595,7 +11587,7 @@
       </c>
       <c r="N173" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -11886,17 +11878,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -11965,10 +11957,33 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+      <c r="G5" s="20" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr"/>
+      <c r="I5" s="20" t="inlineStr"/>
+      <c r="J5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>28&amp;29</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 757呎 (3房)
 -
@@ -11976,7 +11991,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 746呎 (3房)
 -
@@ -11984,8 +11999,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr"/>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>D | 644呎 (2房)
 -
@@ -11993,34 +12008,11 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr"/>
-      <c r="G5" s="21" t="inlineStr"/>
-      <c r="H5" s="21" t="inlineStr"/>
-      <c r="I5" s="21" t="inlineStr"/>
-      <c r="J5" s="21" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>C | 286呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr"/>
-      <c r="I6" s="21" t="inlineStr"/>
-      <c r="J6" s="21" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -12028,7 +12020,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12044,7 +12036,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12068,7 +12060,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12076,7 +12068,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12084,8 +12076,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I7" s="21" t="inlineStr"/>
-      <c r="J7" s="21" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
+      <c r="J7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -12093,7 +12085,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12109,7 +12101,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12133,7 +12125,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12141,7 +12133,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12149,8 +12141,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I8" s="21" t="inlineStr"/>
-      <c r="J8" s="21" t="inlineStr"/>
+      <c r="I8" s="20" t="inlineStr"/>
+      <c r="J8" s="20" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -12174,7 +12166,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12198,7 +12190,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12206,7 +12198,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12214,8 +12206,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I9" s="21" t="inlineStr"/>
-      <c r="J9" s="21" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -12263,7 +12255,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12271,7 +12263,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12279,8 +12271,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I10" s="21" t="inlineStr"/>
-      <c r="J10" s="21" t="inlineStr"/>
+      <c r="I10" s="20" t="inlineStr"/>
+      <c r="J10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -12328,7 +12320,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12336,7 +12328,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12344,8 +12336,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I11" s="21" t="inlineStr"/>
-      <c r="J11" s="21" t="inlineStr"/>
+      <c r="I11" s="20" t="inlineStr"/>
+      <c r="J11" s="20" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -12369,12 +12361,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 $1439万
 $33,005/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -12393,7 +12385,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12401,7 +12393,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12409,8 +12401,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I12" s="21" t="inlineStr"/>
-      <c r="J12" s="21" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -12466,7 +12458,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H13" s="20" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12474,8 +12466,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I13" s="21" t="inlineStr"/>
-      <c r="J13" s="21" t="inlineStr"/>
+      <c r="I13" s="20" t="inlineStr"/>
+      <c r="J13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -12499,12 +12491,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 $1385万
 $31,764/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
@@ -12531,7 +12523,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12539,8 +12531,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr"/>
-      <c r="J14" s="21" t="inlineStr"/>
+      <c r="I14" s="20" t="inlineStr"/>
+      <c r="J14" s="20" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -12604,8 +12596,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I15" s="21" t="inlineStr"/>
-      <c r="J15" s="21" t="inlineStr"/>
+      <c r="I15" s="20" t="inlineStr"/>
+      <c r="J15" s="20" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -12669,8 +12661,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I16" s="21" t="inlineStr"/>
-      <c r="J16" s="21" t="inlineStr"/>
+      <c r="I16" s="20" t="inlineStr"/>
+      <c r="J16" s="20" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -12734,8 +12726,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I17" s="21" t="inlineStr"/>
-      <c r="J17" s="21" t="inlineStr"/>
+      <c r="I17" s="20" t="inlineStr"/>
+      <c r="J17" s="20" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -12799,8 +12791,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I18" s="21" t="inlineStr"/>
-      <c r="J18" s="21" t="inlineStr"/>
+      <c r="I18" s="20" t="inlineStr"/>
+      <c r="J18" s="20" t="inlineStr"/>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
@@ -12864,8 +12856,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I19" s="21" t="inlineStr"/>
-      <c r="J19" s="21" t="inlineStr"/>
+      <c r="I19" s="20" t="inlineStr"/>
+      <c r="J19" s="20" t="inlineStr"/>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
@@ -12905,7 +12897,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F20" s="20" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 296呎 (1房)
 -
@@ -12929,8 +12921,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr"/>
-      <c r="J20" s="21" t="inlineStr"/>
+      <c r="I20" s="20" t="inlineStr"/>
+      <c r="J20" s="20" t="inlineStr"/>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
@@ -13491,7 +13483,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 350呎 (2房)
 -
@@ -13499,7 +13491,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 204呎 (1房)
 -
@@ -13515,15 +13507,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E28" s="23" t="inlineStr">
+      <c r="E28" s="24" t="inlineStr">
         <is>
           <t>D | 234呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F28" s="20" t="inlineStr">
+$622万
+$26,603/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 238呎 (1房)
 -
@@ -13555,7 +13547,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="J28" s="20" t="inlineStr">
+      <c r="J28" s="21" t="inlineStr">
         <is>
           <t>J | 199呎 (开放式)
 -

--- a/港岛-香港仔及鸭脷洲-PORTO/PORTO_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-PORTO/PORTO_销控明细表.xlsx
@@ -271,10 +271,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -11957,12 +11957,49 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 746呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 644呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+      <c r="I5" s="21" t="inlineStr"/>
+      <c r="J5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 286呎 (1房)
 -
@@ -11970,49 +12007,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr"/>
-      <c r="F5" s="20" t="inlineStr"/>
-      <c r="G5" s="20" t="inlineStr"/>
-      <c r="H5" s="20" t="inlineStr"/>
-      <c r="I5" s="20" t="inlineStr"/>
-      <c r="J5" s="20" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>28&amp;29</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 746呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>D | 644呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+      <c r="I6" s="21" t="inlineStr"/>
+      <c r="J6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -12020,7 +12020,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12036,7 +12036,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12060,7 +12060,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12068,7 +12068,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12076,8 +12076,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr"/>
-      <c r="J7" s="20" t="inlineStr"/>
+      <c r="I7" s="21" t="inlineStr"/>
+      <c r="J7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -12085,7 +12085,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12101,7 +12101,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12125,7 +12125,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12133,7 +12133,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12141,8 +12141,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I8" s="20" t="inlineStr"/>
-      <c r="J8" s="20" t="inlineStr"/>
+      <c r="I8" s="21" t="inlineStr"/>
+      <c r="J8" s="21" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -12166,7 +12166,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12190,7 +12190,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12198,7 +12198,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12206,8 +12206,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr"/>
-      <c r="J9" s="20" t="inlineStr"/>
+      <c r="I9" s="21" t="inlineStr"/>
+      <c r="J9" s="21" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -12255,7 +12255,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12263,7 +12263,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12271,8 +12271,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I10" s="20" t="inlineStr"/>
-      <c r="J10" s="20" t="inlineStr"/>
+      <c r="I10" s="21" t="inlineStr"/>
+      <c r="J10" s="21" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -12320,7 +12320,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12328,7 +12328,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12336,8 +12336,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I11" s="20" t="inlineStr"/>
-      <c r="J11" s="20" t="inlineStr"/>
+      <c r="I11" s="21" t="inlineStr"/>
+      <c r="J11" s="21" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -12385,7 +12385,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12393,7 +12393,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12401,8 +12401,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr"/>
-      <c r="J12" s="20" t="inlineStr"/>
+      <c r="I12" s="21" t="inlineStr"/>
+      <c r="J12" s="21" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -12458,7 +12458,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12466,8 +12466,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I13" s="20" t="inlineStr"/>
-      <c r="J13" s="20" t="inlineStr"/>
+      <c r="I13" s="21" t="inlineStr"/>
+      <c r="J13" s="21" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -12523,7 +12523,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H14" s="21" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12531,8 +12531,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I14" s="20" t="inlineStr"/>
-      <c r="J14" s="20" t="inlineStr"/>
+      <c r="I14" s="21" t="inlineStr"/>
+      <c r="J14" s="21" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -12596,8 +12596,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I15" s="20" t="inlineStr"/>
-      <c r="J15" s="20" t="inlineStr"/>
+      <c r="I15" s="21" t="inlineStr"/>
+      <c r="J15" s="21" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -12661,8 +12661,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I16" s="20" t="inlineStr"/>
-      <c r="J16" s="20" t="inlineStr"/>
+      <c r="I16" s="21" t="inlineStr"/>
+      <c r="J16" s="21" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -12726,8 +12726,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I17" s="20" t="inlineStr"/>
-      <c r="J17" s="20" t="inlineStr"/>
+      <c r="I17" s="21" t="inlineStr"/>
+      <c r="J17" s="21" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -12791,8 +12791,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I18" s="20" t="inlineStr"/>
-      <c r="J18" s="20" t="inlineStr"/>
+      <c r="I18" s="21" t="inlineStr"/>
+      <c r="J18" s="21" t="inlineStr"/>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
@@ -12856,8 +12856,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I19" s="20" t="inlineStr"/>
-      <c r="J19" s="20" t="inlineStr"/>
+      <c r="I19" s="21" t="inlineStr"/>
+      <c r="J19" s="21" t="inlineStr"/>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
@@ -12897,7 +12897,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 296呎 (1房)
 -
@@ -12921,8 +12921,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I20" s="20" t="inlineStr"/>
-      <c r="J20" s="20" t="inlineStr"/>
+      <c r="I20" s="21" t="inlineStr"/>
+      <c r="J20" s="21" t="inlineStr"/>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
@@ -12959,7 +12959,7 @@
           <t>D | 271呎 (1房)
 $625万
 $23,055/呎
-(26年-09月-02日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="F21" s="24" t="inlineStr">
@@ -13483,7 +13483,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 350呎 (2房)
 -
@@ -13491,7 +13491,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 204呎 (1房)
 -
@@ -13515,7 +13515,7 @@
 (26年-09月-16日)</t>
         </is>
       </c>
-      <c r="F28" s="21" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 238呎 (1房)
 -
@@ -13547,7 +13547,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="J28" s="21" t="inlineStr">
+      <c r="J28" s="20" t="inlineStr">
         <is>
           <t>J | 199呎 (开放式)
 -

--- a/港岛-香港仔及鸭脷洲-PORTO/PORTO_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-PORTO/PORTO_销控明细表.xlsx
@@ -271,10 +271,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7051,34 +7051,34 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
-        <v>7555000</v>
+        <v>6308000</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>27981</v>
+        <v>23363</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K101" s="5" t="n">
-        <v>6308425</v>
+        <v>6308000</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>23365</v>
+        <v>23363</v>
       </c>
       <c r="M101" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N101" s="3" t="inlineStr">
@@ -11878,7 +11878,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -11888,7 +11888,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -11957,10 +11957,33 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+      <c r="G5" s="20" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr"/>
+      <c r="I5" s="20" t="inlineStr"/>
+      <c r="J5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>28&amp;29</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 757呎 (3房)
 -
@@ -11968,7 +11991,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 746呎 (3房)
 -
@@ -11976,8 +11999,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr"/>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>D | 644呎 (2房)
 -
@@ -11985,34 +12008,11 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr"/>
-      <c r="G5" s="21" t="inlineStr"/>
-      <c r="H5" s="21" t="inlineStr"/>
-      <c r="I5" s="21" t="inlineStr"/>
-      <c r="J5" s="21" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>C | 286呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr"/>
-      <c r="I6" s="21" t="inlineStr"/>
-      <c r="J6" s="21" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -12020,7 +12020,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12036,7 +12036,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12060,7 +12060,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12068,7 +12068,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12076,8 +12076,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I7" s="21" t="inlineStr"/>
-      <c r="J7" s="21" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
+      <c r="J7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -12085,7 +12085,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12101,7 +12101,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12125,7 +12125,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12133,7 +12133,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12141,8 +12141,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I8" s="21" t="inlineStr"/>
-      <c r="J8" s="21" t="inlineStr"/>
+      <c r="I8" s="20" t="inlineStr"/>
+      <c r="J8" s="20" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -12166,7 +12166,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12190,7 +12190,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12198,7 +12198,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12206,8 +12206,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I9" s="21" t="inlineStr"/>
-      <c r="J9" s="21" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -12255,7 +12255,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12263,7 +12263,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12271,8 +12271,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I10" s="21" t="inlineStr"/>
-      <c r="J10" s="21" t="inlineStr"/>
+      <c r="I10" s="20" t="inlineStr"/>
+      <c r="J10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -12320,7 +12320,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12328,7 +12328,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12336,8 +12336,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I11" s="21" t="inlineStr"/>
-      <c r="J11" s="21" t="inlineStr"/>
+      <c r="I11" s="20" t="inlineStr"/>
+      <c r="J11" s="20" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -12385,7 +12385,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12393,7 +12393,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12401,8 +12401,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I12" s="21" t="inlineStr"/>
-      <c r="J12" s="21" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -12458,7 +12458,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H13" s="20" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12466,8 +12466,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I13" s="21" t="inlineStr"/>
-      <c r="J13" s="21" t="inlineStr"/>
+      <c r="I13" s="20" t="inlineStr"/>
+      <c r="J13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -12523,7 +12523,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12531,8 +12531,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr"/>
-      <c r="J14" s="21" t="inlineStr"/>
+      <c r="I14" s="20" t="inlineStr"/>
+      <c r="J14" s="20" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -12596,8 +12596,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I15" s="21" t="inlineStr"/>
-      <c r="J15" s="21" t="inlineStr"/>
+      <c r="I15" s="20" t="inlineStr"/>
+      <c r="J15" s="20" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -12661,8 +12661,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I16" s="21" t="inlineStr"/>
-      <c r="J16" s="21" t="inlineStr"/>
+      <c r="I16" s="20" t="inlineStr"/>
+      <c r="J16" s="20" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -12726,8 +12726,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I17" s="21" t="inlineStr"/>
-      <c r="J17" s="21" t="inlineStr"/>
+      <c r="I17" s="20" t="inlineStr"/>
+      <c r="J17" s="20" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -12791,8 +12791,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I18" s="21" t="inlineStr"/>
-      <c r="J18" s="21" t="inlineStr"/>
+      <c r="I18" s="20" t="inlineStr"/>
+      <c r="J18" s="20" t="inlineStr"/>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
@@ -12856,8 +12856,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I19" s="21" t="inlineStr"/>
-      <c r="J19" s="21" t="inlineStr"/>
+      <c r="I19" s="20" t="inlineStr"/>
+      <c r="J19" s="20" t="inlineStr"/>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
@@ -12889,15 +12889,15 @@
 (26年-06月-04日)</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>D | 270呎 (1房)
-$756万
-$27,981/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F20" s="20" t="inlineStr">
+$631万
+$23,363/呎
+(26年-09月-24日)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 296呎 (1房)
 -
@@ -12921,8 +12921,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr"/>
-      <c r="J20" s="21" t="inlineStr"/>
+      <c r="I20" s="20" t="inlineStr"/>
+      <c r="J20" s="20" t="inlineStr"/>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
@@ -13483,7 +13483,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 350呎 (2房)
 -
@@ -13491,7 +13491,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 204呎 (1房)
 -
@@ -13515,7 +13515,7 @@
 (26年-09月-16日)</t>
         </is>
       </c>
-      <c r="F28" s="20" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 238呎 (1房)
 -
@@ -13547,7 +13547,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="J28" s="20" t="inlineStr">
+      <c r="J28" s="21" t="inlineStr">
         <is>
           <t>J | 199呎 (开放式)
 -

--- a/港岛-香港仔及鸭脷洲-PORTO/PORTO_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-PORTO/PORTO_销控明细表.xlsx
@@ -271,10 +271,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6167,34 +6167,34 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
-        <v>7723000</v>
+        <v>6391000</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>28604</v>
+        <v>23670</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K87" s="5" t="n">
-        <v>6448705</v>
+        <v>6391000</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>23884</v>
+        <v>23670</v>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N87" s="3" t="inlineStr">
@@ -11878,7 +11878,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -11888,7 +11888,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>71</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -11957,12 +11957,49 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 746呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 644呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+      <c r="I5" s="21" t="inlineStr"/>
+      <c r="J5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 286呎 (1房)
 -
@@ -11970,49 +12007,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr"/>
-      <c r="F5" s="20" t="inlineStr"/>
-      <c r="G5" s="20" t="inlineStr"/>
-      <c r="H5" s="20" t="inlineStr"/>
-      <c r="I5" s="20" t="inlineStr"/>
-      <c r="J5" s="20" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>28&amp;29</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 746呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>D | 644呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+      <c r="I6" s="21" t="inlineStr"/>
+      <c r="J6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -12020,7 +12020,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12036,7 +12036,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12060,7 +12060,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12068,7 +12068,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12076,8 +12076,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr"/>
-      <c r="J7" s="20" t="inlineStr"/>
+      <c r="I7" s="21" t="inlineStr"/>
+      <c r="J7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -12085,7 +12085,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12101,7 +12101,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12125,7 +12125,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12133,7 +12133,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12141,8 +12141,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I8" s="20" t="inlineStr"/>
-      <c r="J8" s="20" t="inlineStr"/>
+      <c r="I8" s="21" t="inlineStr"/>
+      <c r="J8" s="21" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -12166,7 +12166,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12190,7 +12190,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12198,7 +12198,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12206,8 +12206,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr"/>
-      <c r="J9" s="20" t="inlineStr"/>
+      <c r="I9" s="21" t="inlineStr"/>
+      <c r="J9" s="21" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -12255,7 +12255,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12263,7 +12263,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12271,8 +12271,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I10" s="20" t="inlineStr"/>
-      <c r="J10" s="20" t="inlineStr"/>
+      <c r="I10" s="21" t="inlineStr"/>
+      <c r="J10" s="21" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -12320,7 +12320,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12328,7 +12328,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12336,8 +12336,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I11" s="20" t="inlineStr"/>
-      <c r="J11" s="20" t="inlineStr"/>
+      <c r="I11" s="21" t="inlineStr"/>
+      <c r="J11" s="21" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -12385,7 +12385,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12393,7 +12393,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12401,8 +12401,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr"/>
-      <c r="J12" s="20" t="inlineStr"/>
+      <c r="I12" s="21" t="inlineStr"/>
+      <c r="J12" s="21" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -12458,7 +12458,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12466,8 +12466,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I13" s="20" t="inlineStr"/>
-      <c r="J13" s="20" t="inlineStr"/>
+      <c r="I13" s="21" t="inlineStr"/>
+      <c r="J13" s="21" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -12523,7 +12523,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H14" s="21" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12531,8 +12531,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I14" s="20" t="inlineStr"/>
-      <c r="J14" s="20" t="inlineStr"/>
+      <c r="I14" s="21" t="inlineStr"/>
+      <c r="J14" s="21" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -12596,8 +12596,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I15" s="20" t="inlineStr"/>
-      <c r="J15" s="20" t="inlineStr"/>
+      <c r="I15" s="21" t="inlineStr"/>
+      <c r="J15" s="21" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -12661,8 +12661,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I16" s="20" t="inlineStr"/>
-      <c r="J16" s="20" t="inlineStr"/>
+      <c r="I16" s="21" t="inlineStr"/>
+      <c r="J16" s="21" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -12726,8 +12726,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I17" s="20" t="inlineStr"/>
-      <c r="J17" s="20" t="inlineStr"/>
+      <c r="I17" s="21" t="inlineStr"/>
+      <c r="J17" s="21" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -12759,12 +12759,12 @@
 (26年-09月-13日)</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E18" s="24" t="inlineStr">
         <is>
           <t>D | 270呎 (1房)
-$772万
-$28,604/呎
-(在售)</t>
+$639万
+$23,670/呎
+(26年-09月-27日)</t>
         </is>
       </c>
       <c r="F18" s="24" t="inlineStr">
@@ -12791,8 +12791,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I18" s="20" t="inlineStr"/>
-      <c r="J18" s="20" t="inlineStr"/>
+      <c r="I18" s="21" t="inlineStr"/>
+      <c r="J18" s="21" t="inlineStr"/>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
@@ -12856,8 +12856,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I19" s="20" t="inlineStr"/>
-      <c r="J19" s="20" t="inlineStr"/>
+      <c r="I19" s="21" t="inlineStr"/>
+      <c r="J19" s="21" t="inlineStr"/>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
@@ -12897,7 +12897,7 @@
 (26年-09月-24日)</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 296呎 (1房)
 -
@@ -12921,8 +12921,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I20" s="20" t="inlineStr"/>
-      <c r="J20" s="20" t="inlineStr"/>
+      <c r="I20" s="21" t="inlineStr"/>
+      <c r="J20" s="21" t="inlineStr"/>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
@@ -13483,7 +13483,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 350呎 (2房)
 -
@@ -13491,7 +13491,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="21" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 204呎 (1房)
 -
@@ -13515,7 +13515,7 @@
 (26年-09月-16日)</t>
         </is>
       </c>
-      <c r="F28" s="21" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 238呎 (1房)
 -
@@ -13547,7 +13547,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="J28" s="21" t="inlineStr">
+      <c r="J28" s="20" t="inlineStr">
         <is>
           <t>J | 199呎 (开放式)
 -

--- a/港岛-香港仔及鸭脷洲-PORTO/PORTO_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-PORTO/PORTO_销控明细表.xlsx
@@ -4555,34 +4555,34 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
-        <v>8188000</v>
+        <v>6837000</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>33975</v>
+        <v>28369</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="5" t="n">
-        <v>6836980</v>
+        <v>6837000</v>
       </c>
       <c r="L61" s="5" t="n">
         <v>28369</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -7671,34 +7671,34 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
-        <v>12460000</v>
+        <v>10404000</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>28447</v>
+        <v>23753</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K111" s="5" t="n">
-        <v>10404100</v>
+        <v>10404000</v>
       </c>
       <c r="L111" s="5" t="n">
-        <v>23754</v>
+        <v>23753</v>
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
-          <t>建築期付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N111" s="3" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11878,7 +11878,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -11888,7 +11888,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -12483,12 +12483,12 @@
 (26年-06月-08日)</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>B | 241呎 (1房)
-$819万
-$33,975/呎
-(在售)</t>
+$684万
+$28,369/呎
+(26年-10月-01日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -12561,7 +12561,7 @@
           <t>C | 436呎 (2房)
 $1140万
 $26,138/呎
-(26年-09月-12日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -12946,12 +12946,12 @@
 (26年-05月-26日)</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D21" s="24" t="inlineStr">
         <is>
           <t>C | 438呎 (2房)
-$1246万
-$28,447/呎
-(在售)</t>
+$1040万
+$23,753/呎
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="E21" s="24" t="inlineStr">
@@ -13512,7 +13512,7 @@
           <t>D | 234呎 (1房)
 $622万
 $26,603/呎
-(26年-09月-16日)</t>
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">

--- a/港岛-香港仔及鸭脷洲-PORTO/PORTO_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-PORTO/PORTO_销控明细表.xlsx
@@ -271,10 +271,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -11957,10 +11957,33 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 286呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+      <c r="G5" s="20" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr"/>
+      <c r="I5" s="20" t="inlineStr"/>
+      <c r="J5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>28&amp;29</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 757呎 (3房)
 -
@@ -11968,7 +11991,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 746呎 (3房)
 -
@@ -11976,8 +11999,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr"/>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>D | 644呎 (2房)
 -
@@ -11985,34 +12008,11 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr"/>
-      <c r="G5" s="21" t="inlineStr"/>
-      <c r="H5" s="21" t="inlineStr"/>
-      <c r="I5" s="21" t="inlineStr"/>
-      <c r="J5" s="21" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>C | 286呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr"/>
-      <c r="I6" s="21" t="inlineStr"/>
-      <c r="J6" s="21" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -12020,7 +12020,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12036,7 +12036,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12060,7 +12060,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12068,7 +12068,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12076,8 +12076,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I7" s="21" t="inlineStr"/>
-      <c r="J7" s="21" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
+      <c r="J7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -12085,7 +12085,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 388呎 (2房)
 -
@@ -12101,7 +12101,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12125,7 +12125,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12133,7 +12133,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H8" s="20" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12141,8 +12141,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I8" s="21" t="inlineStr"/>
-      <c r="J8" s="21" t="inlineStr"/>
+      <c r="I8" s="20" t="inlineStr"/>
+      <c r="J8" s="20" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -12166,7 +12166,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 436呎 (2房)
 -
@@ -12190,7 +12190,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12198,7 +12198,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12206,8 +12206,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I9" s="21" t="inlineStr"/>
-      <c r="J9" s="21" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
@@ -12255,7 +12255,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12263,7 +12263,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12271,8 +12271,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I10" s="21" t="inlineStr"/>
-      <c r="J10" s="21" t="inlineStr"/>
+      <c r="I10" s="20" t="inlineStr"/>
+      <c r="J10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -12320,7 +12320,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12328,7 +12328,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12336,8 +12336,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I11" s="21" t="inlineStr"/>
-      <c r="J11" s="21" t="inlineStr"/>
+      <c r="I11" s="20" t="inlineStr"/>
+      <c r="J11" s="20" t="inlineStr"/>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
@@ -12385,7 +12385,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>F | 384呎 (2房)
 -
@@ -12393,7 +12393,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12401,8 +12401,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I12" s="21" t="inlineStr"/>
-      <c r="J12" s="21" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
@@ -12458,7 +12458,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H13" s="20" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12466,8 +12466,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I13" s="21" t="inlineStr"/>
-      <c r="J13" s="21" t="inlineStr"/>
+      <c r="I13" s="20" t="inlineStr"/>
+      <c r="J13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
@@ -12523,7 +12523,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>G | 219呎 (开放式)
 -
@@ -12531,8 +12531,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr"/>
-      <c r="J14" s="21" t="inlineStr"/>
+      <c r="I14" s="20" t="inlineStr"/>
+      <c r="J14" s="20" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
@@ -12596,8 +12596,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I15" s="21" t="inlineStr"/>
-      <c r="J15" s="21" t="inlineStr"/>
+      <c r="I15" s="20" t="inlineStr"/>
+      <c r="J15" s="20" t="inlineStr"/>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
@@ -12661,8 +12661,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I16" s="21" t="inlineStr"/>
-      <c r="J16" s="21" t="inlineStr"/>
+      <c r="I16" s="20" t="inlineStr"/>
+      <c r="J16" s="20" t="inlineStr"/>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
@@ -12726,8 +12726,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I17" s="21" t="inlineStr"/>
-      <c r="J17" s="21" t="inlineStr"/>
+      <c r="I17" s="20" t="inlineStr"/>
+      <c r="J17" s="20" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
@@ -12756,7 +12756,7 @@
           <t>C | 436呎 (2房)
 $1067万
 $24,482/呎
-(26年-09月-13日)</t>
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="E18" s="24" t="inlineStr">
@@ -12791,8 +12791,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I18" s="21" t="inlineStr"/>
-      <c r="J18" s="21" t="inlineStr"/>
+      <c r="I18" s="20" t="inlineStr"/>
+      <c r="J18" s="20" t="inlineStr"/>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
@@ -12856,8 +12856,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I19" s="21" t="inlineStr"/>
-      <c r="J19" s="21" t="inlineStr"/>
+      <c r="I19" s="20" t="inlineStr"/>
+      <c r="J19" s="20" t="inlineStr"/>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
@@ -12894,10 +12894,10 @@
           <t>D | 270呎 (1房)
 $631万
 $23,363/呎
-(26年-09月-24日)</t>
-        </is>
-      </c>
-      <c r="F20" s="20" t="inlineStr">
+(26年-10月-15日)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 296呎 (1房)
 -
@@ -12921,8 +12921,8 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr"/>
-      <c r="J20" s="21" t="inlineStr"/>
+      <c r="I20" s="20" t="inlineStr"/>
+      <c r="J20" s="20" t="inlineStr"/>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
@@ -13483,7 +13483,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 350呎 (2房)
 -
@@ -13491,7 +13491,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 204呎 (1房)
 -
@@ -13515,7 +13515,7 @@
 (26年-10月-02日)</t>
         </is>
       </c>
-      <c r="F28" s="20" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 238呎 (1房)
 -
@@ -13547,7 +13547,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="J28" s="20" t="inlineStr">
+      <c r="J28" s="21" t="inlineStr">
         <is>
           <t>J | 199呎 (开放式)
 -

--- a/港岛-香港仔及鸭脷洲-PORTO/PORTO_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-PORTO/PORTO_销控明细表.xlsx
@@ -4560,7 +4560,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -12488,7 +12488,7 @@
           <t>B | 241呎 (1房)
 $684万
 $28,369/呎
-(26年-10月-01日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -12764,7 +12764,7 @@
           <t>D | 270呎 (1房)
 $639万
 $23,670/呎
-(26年-09月-27日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="F18" s="24" t="inlineStr">
@@ -12951,7 +12951,7 @@
           <t>C | 438呎 (2房)
 $1040万
 $23,753/呎
-(26年-10月-02日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="E21" s="24" t="inlineStr">
